--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="423">
   <si>
     <t>Property</t>
   </si>
@@ -810,10 +810,10 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:dentaloral</t>
-  </si>
-  <si>
-    <t>dentaloral</t>
+    <t>DiagnosticReport.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
   </si>
   <si>
     <t>診断レポートを作成した臨床分野、部門、または診断サービス（心臓病学、生化学、血液学、放射線医学など）を分類するコード</t>
@@ -825,43 +825,43 @@
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:dentaloral.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:dentaloral.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:dentaloral.coding</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:dentaloral.coding.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:dentaloral.coding.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:dentaloral.coding.system</t>
+    <t>DiagnosticReport.category:first.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.system</t>
   </si>
   <si>
     <t>http://loinc.org</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:dentaloral.coding.version</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:dentaloral.coding.code</t>
+    <t>DiagnosticReport.category:first.coding.version</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.code</t>
   </si>
   <si>
     <t>LP31759-1</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:dentaloral.coding.display</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:dentaloral.coding.userSelected</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:dentaloral.text</t>
+    <t>DiagnosticReport.category:first.coding.display</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.userSelected</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.text</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -903,6 +903,9 @@
   </si>
   <si>
     <t>DiagnosticReport.code.coding:dentaloral</t>
+  </si>
+  <si>
+    <t>dentaloral</t>
   </si>
   <si>
     <t>DiagnosticReport.code.coding:dentaloral.id</t>
@@ -1640,7 +1643,7 @@
   <dimension ref="A1:AN68"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="54.7421875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="51.0625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.8125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
@@ -6375,7 +6378,7 @@
         <v>283</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>81</v>
@@ -6487,10 +6490,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6599,10 +6602,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6713,10 +6716,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6742,10 +6745,10 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>214</v>
@@ -6758,7 +6761,7 @@
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>81</v>
@@ -6829,10 +6832,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6943,10 +6946,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6972,10 +6975,10 @@
         <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
@@ -6986,7 +6989,7 @@
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>81</v>
@@ -7057,10 +7060,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7086,10 +7089,10 @@
         <v>191</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
@@ -7171,10 +7174,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7287,10 +7290,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7403,14 +7406,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7429,19 +7432,19 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -7490,7 +7493,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7505,28 +7508,28 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7545,19 +7548,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7606,7 +7609,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7621,28 +7624,28 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7661,19 +7664,19 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -7722,7 +7725,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7737,28 +7740,28 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7777,19 +7780,19 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -7838,7 +7841,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7856,25 +7859,25 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7893,19 +7896,19 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -7954,7 +7957,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7969,28 +7972,28 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8009,19 +8012,19 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8070,7 +8073,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8085,24 +8088,24 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8125,19 +8128,19 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8186,7 +8189,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8204,10 +8207,10 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
@@ -8215,14 +8218,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8241,19 +8244,19 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8302,7 +8305,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8320,10 +8323,10 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -8331,10 +8334,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8357,16 +8360,16 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8416,7 +8419,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8437,7 +8440,7 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
@@ -8445,14 +8448,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8471,19 +8474,19 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -8532,7 +8535,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8550,10 +8553,10 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
@@ -8561,10 +8564,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8673,10 +8676,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8787,14 +8790,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8816,10 +8819,10 @@
         <v>137</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>140</v>
@@ -8874,7 +8877,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8903,10 +8906,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8932,16 +8935,16 @@
         <v>191</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -8990,7 +8993,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9011,7 +9014,7 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -9019,10 +9022,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9045,13 +9048,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9102,7 +9105,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -9123,7 +9126,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -9131,14 +9134,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9160,14 +9163,14 @@
         <v>191</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -9216,7 +9219,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9234,10 +9237,10 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -9245,10 +9248,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9274,13 +9277,13 @@
         <v>179</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9309,10 +9312,10 @@
         <v>182</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -9330,7 +9333,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9348,10 +9351,10 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -9359,10 +9362,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9385,19 +9388,19 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -9446,7 +9449,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9464,10 +9467,10 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="395">
   <si>
     <t>Property</t>
   </si>
@@ -874,6 +874,15 @@
     <t>診断レポート種別「口腔診査報告書」を表す文書コード</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_DocumentCodes_CS"/&gt;
+    &lt;code value="32453-3"/&gt;
+    &lt;display value="口腔診査報告書"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_DiagnosticReport_VS</t>
   </si>
   <si>
@@ -887,94 +896,6 @@
   </si>
   <si>
     <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:coding.system}
-</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding:dentaloral</t>
-  </si>
-  <si>
-    <t>dentaloral</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding:dentaloral.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding:dentaloral.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding:dentaloral.system</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding.system</t>
-  </si>
-  <si>
-    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DocumentCodes_CS</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding:dentaloral.version</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding.version</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding:dentaloral.code</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding.code</t>
-  </si>
-  <si>
-    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>32453-3</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding:dentaloral.display</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding.display</t>
-  </si>
-  <si>
-    <t>システムによって定義された表現 / Representation defined by the system</t>
-  </si>
-  <si>
-    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding:dentaloral.userSelected</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.text</t>
   </si>
   <si>
     <t>DiagnosticReport.subject</t>
@@ -1640,10 +1561,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN68"/>
+  <dimension ref="A1:AN56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.0625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.01171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.8125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
@@ -5966,7 +5887,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -5985,7 +5906,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6018,28 +5939,28 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>81</v>
+        <v>283</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6055,19 +5976,23 @@
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>191</v>
+        <v>284</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>192</v>
+        <v>285</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6115,7 +6040,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>194</v>
+        <v>282</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6127,38 +6052,38 @@
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>81</v>
+        <v>288</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>195</v>
+        <v>290</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>81</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>136</v>
+        <v>293</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6167,21 +6092,23 @@
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>137</v>
+        <v>294</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>138</v>
+        <v>295</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>197</v>
+        <v>295</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6217,62 +6144,62 @@
         <v>81</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>198</v>
+        <v>81</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>199</v>
+        <v>81</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>186</v>
+        <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>200</v>
+        <v>292</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>81</v>
+        <v>298</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>195</v>
+        <v>300</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>81</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>81</v>
+        <v>303</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G41" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -6284,19 +6211,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>202</v>
+        <v>304</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>203</v>
+        <v>305</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>204</v>
+        <v>305</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>205</v>
+        <v>306</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>206</v>
+        <v>307</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6333,23 +6260,25 @@
         <v>81</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>186</v>
+        <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>207</v>
+        <v>302</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -6358,34 +6287,32 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>81</v>
+        <v>308</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>208</v>
+        <v>309</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>209</v>
+        <v>310</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>91</v>
@@ -6400,19 +6327,19 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>202</v>
+        <v>314</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>203</v>
+        <v>315</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>204</v>
+        <v>315</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>205</v>
+        <v>316</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>206</v>
+        <v>317</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6461,13 +6388,13 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>207</v>
+        <v>312</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>81</v>
@@ -6479,32 +6406,32 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>208</v>
+        <v>318</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>209</v>
+        <v>319</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>81</v>
+        <v>320</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>287</v>
+        <v>321</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>288</v>
+        <v>321</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>81</v>
+        <v>322</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -6513,19 +6440,23 @@
         <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>191</v>
+        <v>323</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>192</v>
+        <v>324</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -6573,43 +6504,43 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>194</v>
+        <v>321</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>81</v>
+        <v>327</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>81</v>
+        <v>328</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>195</v>
+        <v>329</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>81</v>
+        <v>330</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>289</v>
+        <v>331</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>290</v>
+        <v>331</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>136</v>
+        <v>332</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6625,21 +6556,23 @@
         <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>137</v>
+        <v>323</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>138</v>
+        <v>333</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>197</v>
+        <v>333</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
@@ -6675,19 +6608,19 @@
         <v>81</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>198</v>
+        <v>81</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>199</v>
+        <v>81</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>186</v>
+        <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>200</v>
+        <v>331</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6699,27 +6632,27 @@
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>81</v>
+        <v>327</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>195</v>
+        <v>329</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>81</v>
+        <v>330</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>291</v>
+        <v>336</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>292</v>
+        <v>336</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6730,7 +6663,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -6739,29 +6672,29 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>105</v>
+        <v>337</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>294</v>
+        <v>338</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>214</v>
+        <v>339</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>215</v>
+        <v>340</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>295</v>
+        <v>81</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>81</v>
@@ -6803,13 +6736,13 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>216</v>
+        <v>336</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
@@ -6821,10 +6754,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>217</v>
+        <v>341</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>218</v>
+        <v>290</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -6832,21 +6765,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>296</v>
+        <v>342</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>297</v>
+        <v>342</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>81</v>
+        <v>343</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -6855,21 +6788,23 @@
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>191</v>
+        <v>344</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>220</v>
+        <v>345</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>221</v>
+        <v>345</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -6917,13 +6852,13 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>223</v>
+        <v>342</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
@@ -6935,10 +6870,10 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>224</v>
+        <v>348</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>225</v>
+        <v>349</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -6946,10 +6881,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>298</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>299</v>
+        <v>350</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6957,10 +6892,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -6969,27 +6904,27 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>111</v>
+        <v>351</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>300</v>
+        <v>352</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>81</v>
@@ -7031,13 +6966,13 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>229</v>
+        <v>350</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
@@ -7049,10 +6984,10 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>230</v>
+        <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>231</v>
+        <v>354</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7060,21 +6995,21 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>303</v>
+        <v>355</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>304</v>
+        <v>355</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>81</v>
+        <v>356</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7086,17 +7021,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>191</v>
+        <v>357</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>305</v>
+        <v>358</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>234</v>
+        <v>360</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7145,13 +7082,13 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>235</v>
+        <v>355</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
@@ -7163,10 +7100,10 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>236</v>
+        <v>361</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>237</v>
+        <v>349</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7174,10 +7111,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>307</v>
+        <v>362</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>308</v>
+        <v>362</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7197,23 +7134,19 @@
         <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>239</v>
+        <v>191</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>240</v>
+        <v>192</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7261,7 +7194,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>244</v>
+        <v>194</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7273,16 +7206,16 @@
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -7290,21 +7223,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>309</v>
+        <v>363</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>309</v>
+        <v>363</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -7313,23 +7246,21 @@
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>191</v>
+        <v>137</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>248</v>
+        <v>138</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>249</v>
+        <v>197</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -7377,28 +7308,28 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>252</v>
+        <v>200</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>253</v>
+        <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>254</v>
+        <v>195</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -7406,45 +7337,45 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>310</v>
+        <v>364</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>310</v>
+        <v>364</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>312</v>
+        <v>137</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>313</v>
+        <v>366</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>313</v>
+        <v>367</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>314</v>
+        <v>140</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>315</v>
+        <v>146</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -7493,43 +7424,43 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>310</v>
+        <v>368</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>316</v>
+        <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>317</v>
+        <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>318</v>
+        <v>134</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>319</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>320</v>
+        <v>369</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>320</v>
+        <v>369</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>321</v>
+        <v>81</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7545,22 +7476,22 @@
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>322</v>
+        <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>323</v>
+        <v>370</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>323</v>
+        <v>371</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7609,7 +7540,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>320</v>
+        <v>369</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7624,32 +7555,32 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>328</v>
+        <v>374</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>331</v>
+        <v>81</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>91</v>
@@ -7664,20 +7595,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>332</v>
+        <v>376</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>333</v>
+        <v>377</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
@@ -7725,10 +7652,10 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>91</v>
@@ -7740,28 +7667,28 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>337</v>
+        <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>338</v>
+        <v>378</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>339</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>340</v>
+        <v>379</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>340</v>
+        <v>379</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>341</v>
+        <v>380</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7777,22 +7704,20 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>342</v>
+        <v>191</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>345</v>
+        <v>381</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -7841,7 +7766,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>340</v>
+        <v>379</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7859,25 +7784,25 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>346</v>
+        <v>382</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>347</v>
+        <v>383</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>348</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>350</v>
+        <v>81</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7893,23 +7818,21 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>351</v>
+        <v>179</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -7933,13 +7856,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>81</v>
+        <v>386</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>81</v>
+        <v>387</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -7957,7 +7880,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7972,28 +7895,28 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>355</v>
+        <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>357</v>
+        <v>388</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>358</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>360</v>
+        <v>81</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8009,22 +7932,22 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>351</v>
+        <v>390</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>361</v>
+        <v>391</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>361</v>
+        <v>391</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>354</v>
+        <v>393</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8073,7 +7996,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8088,1391 +8011,15 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>355</v>
+        <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>357</v>
+        <v>394</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="P57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="P58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AN68" t="s" s="2">
         <v>81</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -278,7 +278,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -322,16 +322,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -457,7 +457,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -278,7 +278,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="399">
   <si>
     <t>Property</t>
   </si>
@@ -269,12 +269,12 @@
     <t>診断レポート-依頼情報、１項目単位の結果、画像、解釈、およびフォーマットされたレポートの組み合わせ　【JP Core仕様】口腔診査結果レポートのプロフィール</t>
   </si>
   <si>
-    <t>患者、患者のグループ、デバイス、場所、これらから派生した対象に対して実行された診断的検査の結果と解釈。レポートには、依頼情報や依頼者情報などの臨床コンテキスト（文脈）、および１項目単位の結果、画像、テキストとコード化された解釈、および診断レポートのフォーマットされた表現のいくつかの組み合わせが含まれる。
-【JP Core仕様】口腔診査結果レポートのプロフィール</t>
-  </si>
-  <si>
-    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。
-【JP Core仕様】DiagnosticReportリソースの共通プロフィール</t>
+    <t>患者、患者のグループ、デバイス、場所、これらから派生した対象に対して実行された診断的検査の結果と解釈。レポートには、依頼情報や依頼者情報などの臨床コンテキスト（文脈）、および１項目単位の結果、画像、テキストとコード化された解釈、および診断レポートのフォーマットされた表現のいくつかの組み合わせが含まれる。
+【JP Core仕様】口腔診査結果レポートのプロファイル</t>
+  </si>
+  <si>
+    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。
+【JP Core仕様】DiagnosticReportリソースの共通プロファイル</t>
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -489,10 +489,11 @@
 </t>
   </si>
   <si>
-    <t>当該検査項目に対して、施設内で割り振られる一位の識別子があればそちらを使用する。例：電子カルテ等のオーダ番号、レポート番号、実施日に連番を付加した番号など</t>
-  </si>
-  <si>
-    <t>通常、診断サービスプロバイダの情報システム（フィラーID）によって割り当てられる。</t>
+    <t>レポートを識別するビジネス識別子  
+【JP Core仕様】当該検査項目に対して、施設内で割り振られる一位の識別子があればそちらを使用する。</t>
+  </si>
+  <si>
+    <t>例：電子カルテ等のオーダ番号、レポート番号、実施日に連番を付加した番号など</t>
   </si>
   <si>
     <t>発生源の検査室からこのレポートについてクエリを作成するとき、およびFHIRコンテキスト外のレポートにリンクするときに使用する識別子を知る必要がある。</t>
@@ -521,7 +522,8 @@
 </t>
   </si>
   <si>
-    <t>オーダ発生元のServiceRequestまたはCarePlanへの参照</t>
+    <t>元になった検査や診断の依頼  
+【JP Core仕様】オーダ発生元のServiceRequestまたはCarePlanへの参照</t>
   </si>
   <si>
     <t>通常、１結果ごとに１つの検査依頼があるが、状況によっては、複数の検査要求に対して１レポートがある場合がある。また１つの検査依頼に対して複数のレポートが作成される場合もあることに注意。</t>
@@ -542,7 +544,8 @@
     <t>DiagnosticReport.status</t>
   </si>
   <si>
-    <t>診断レポートのステータス。レポートの記載状況をバインディングされたコードセットから必ず一つ選ぶ。</t>
+    <t>診断レポートのステータス  
+【JP Core仕様】レポートの記載状況をバインディングされたコードセットから必ず一つ選ぶ。</t>
   </si>
   <si>
     <t>診断サービスは、暫定/不完全なレポートを日常的に発行し、以前にリリースされたレポートを撤回することもあります。 / Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
@@ -909,7 +912,8 @@
 </t>
   </si>
   <si>
-    <t>Paitientリソースを参照</t>
+    <t>レポートの対象、常にではないが、通常は患者  
+【JP Core仕様】Patientリソースを参照</t>
   </si>
   <si>
     <t>レポートの対象、通常、Patientリソースへの参照。ただし、他のさまざまなソースから収集された検体を対象とすることもある。参照は内容に辿り着ける（解決できる）必要がある（アクセス制御、一時的な使用不可などを考慮に入れる）。解決は、URLから取得するか、リソースタイプによって該当する場合は、絶対参照を正規URLとして扱い、ローカルレジストリ/リポジトリで検索することによって行うことができる。</t>
@@ -941,10 +945,11 @@
 </t>
   </si>
   <si>
-    <t>このレポートを書く切っ掛けとなるEncounterリソースを参照。例：診療、歯科健診（検診）、身元不明者調査</t>
-  </si>
-  <si>
-    <t>受診、入院、診察など。通常、イベントが発生したEncounterであるが、一部のイベントは、Encounterの正式な完了の前または後に開始される場合があり、その場合でもEncounterのコンテキストに関連付けられている（例：入院前の臨床検査）。</t>
+    <t>依頼時におけるヘルスケアイベント（受診など）  
+【JP Core仕様】このレポートを書く切っ掛けとなるEncounterリソースを参照</t>
+  </si>
+  <si>
+    <t>例：診療、歯科健診（検診）、身元不明者調査 ※JP Coreに網羅されていない</t>
   </si>
   <si>
     <t>リクエストをエンカウンターコンテキストにリンクします。 / Links the request to the Encounter context.</t>
@@ -973,7 +978,8 @@
 </t>
   </si>
   <si>
-    <t>レポート作成日時</t>
+    <t>臨床的に関連する時刻または時間  
+【JP Core仕様】レポート作成日時</t>
   </si>
   <si>
     <t>観測値が関連する時間または期間。レポートの対象が患者である場合、これは通常、読影開始の時間であり、日付／時刻自体のみ提供される。実施日時。</t>
@@ -1005,7 +1011,8 @@
 </t>
   </si>
   <si>
-    <t>最新のレポート確定日時</t>
+    <t>このバージョンが作成された日時  
+【JP Core仕様】最新のレポート確定日時</t>
   </si>
   <si>
     <t>通常、レポートがレビューおよび検証・確定された後となる。リソース自体の更新時刻とは異なる場合がある。これは、レポートの実際の提供時刻ではなく、リソース自体の更新時刻はレコード（場合によってはセカンダリコピー）のステータスの更新時刻となるため。</t>
@@ -1034,10 +1041,11 @@
 </t>
   </si>
   <si>
-    <t>レポート確定者。例：歯科医師など</t>
-  </si>
-  <si>
-    <t>必ずしも１項目データ単位のデータソースまたは結果を解釈した主体でなない。臨床レポートに責任をもつ主体のこと。</t>
+    <t>レポート内容に責任をもつ診断的サービス  
+【JP Core仕様】レポート確定者</t>
+  </si>
+  <si>
+    <t>例：歯科医師など</t>
   </si>
   <si>
     <t>結果についてクエリがある場合は、誰に連絡するかを知る必要があります。また、二次データ分析のためにレポートのソースを追跡する必要がある場合があります。 / Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
@@ -1062,10 +1070,11 @@
 Reported by</t>
   </si>
   <si>
-    <t>レポートの作成者。例：歯科医師、歯科研修医など</t>
-  </si>
-  <si>
-    <t>診断レポートに責任を持つもの(performer)とは異なる場合がある。</t>
+    <t>結果の一次解釈者  
+【JP Core仕様】レポートの作成者</t>
+  </si>
+  <si>
+    <t>例：歯科医師、歯科研修医など</t>
   </si>
   <si>
     <t>OBR-32, PRT-8 (where this PRT-4-Participation = "PI")</t>
@@ -1078,7 +1087,8 @@
 </t>
   </si>
   <si>
-    <t>未使用</t>
+    <t>診断レポートのもとになった検体に関する情報  
+【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>検査結果名称のコードを見れば検体情報が十分に判明するような場合には、この検体情報は冗長になる。複数の検体が関与する場合には、検査や検査グループごとに検体情報が記述されることがある。</t>
@@ -1101,7 +1111,8 @@
 </t>
   </si>
   <si>
-    <t>検査結果</t>
+    <t>診断レポートの一部となるObservationsに関する情報  
+【JP Core仕様】検査結果</t>
   </si>
   <si>
     <t>Observationsは階層構造を持てる。</t>
@@ -1123,7 +1134,7 @@
 </t>
   </si>
   <si>
-    <t>診断レポートに関連づけられた画像検査の詳細情報への参照</t>
+    <t>診断レポートに関連づけれられたDICOM検査画像に関する情報</t>
   </si>
   <si>
     <t>診断的精査中に実施された画像検査の詳細情報へのひとつ/複数のリンク。通常は、DICOM対応のモダリティーによって実施される画像検査だが、必須ではない。完全対応のPACSビューワはこの情報を使用して原画像の一覧を提供できる。</t>
@@ -1143,7 +1154,8 @@
 </t>
   </si>
   <si>
-    <t>このレポートに関連づけられたキー画像</t>
+    <t>診断レポートに関連づけられたメディアに関する情報  
+【JP Core仕様】このレポートに関連づけられたキー画像</t>
   </si>
   <si>
     <t>通常は画像。診断プロセス中に作成され、患者から直接取得されたもの、あるいは調製された検体標本（つまり、関心のあるスライド）のこともある。</t>
@@ -1204,6 +1216,12 @@
 </t>
   </si>
   <si>
+    <t>画像ソースへの参照 / Reference to the image source</t>
+  </si>
+  <si>
+    <t>画像ソースへの参照。 / Reference to the image source.</t>
+  </si>
+  <si>
     <t>例：口腔内写真、jpgで保存されている画像、3Dデータなど</t>
   </si>
   <si>
@@ -1217,6 +1235,10 @@
 </t>
   </si>
   <si>
+    <t>簡潔かつ臨床的な文脈で表現した診断レポートの要約結論（解釈、インプレッション）  
+【JP Core仕様】原則、未使用。レセプト傷病名などテキスト型で記載も可能。</t>
+  </si>
+  <si>
     <t>基本的な結果データの中で失われない結論を提供できる必要があります。 / Need to be able to provide a conclusion that is not lost among the basic result data.</t>
   </si>
   <si>
@@ -1227,6 +1249,10 @@
   </si>
   <si>
     <t>DiagnosticReport.conclusionCode</t>
+  </si>
+  <si>
+    <t>診断レポートの要約結論（解釈、インプレッション）を表すコード  
+【JP Core仕様】原則、未使用。レセプト傷病名などのCodeableConcept型で定義も可能。</t>
   </si>
   <si>
     <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、独自の構造を提供する必要がある。</t>
@@ -1248,7 +1274,7 @@
 </t>
   </si>
   <si>
-    <t>発行されたレポート全体</t>
+    <t>診断サービス/担当者によって発行された診断レポート全体のコンテンツ（例えばPDFファイルなど）</t>
   </si>
   <si>
     <t>複数のフォーマットが許可されるが、それらは意味的に同等である必要がある。「application / pdf」がこのコンテキストで最も信頼でき相互運用可能なものとして推奨される。</t>
@@ -7601,9 +7627,11 @@
         <v>377</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -7673,7 +7701,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -7681,14 +7709,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7710,14 +7738,14 @@
         <v>191</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -7766,7 +7794,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7784,10 +7812,10 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -7795,10 +7823,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7824,13 +7852,13 @@
         <v>179</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>338</v>
+        <v>388</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>338</v>
+        <v>388</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7859,28 +7887,28 @@
         <v>182</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="Z55" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7898,10 +7926,10 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -7909,10 +7937,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7935,19 +7963,19 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -7996,7 +8024,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8014,10 +8042,10 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -1590,17 +1590,17 @@
   <dimension ref="A1:AN56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.01171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.8125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.01953125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.41796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="53.34375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="186.66796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="160.03515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1609,26 +1609,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="73.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.203125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="62.875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="171.66796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="121.93359375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="147.17578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="104.53515625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -489,8 +489,7 @@
 </t>
   </si>
   <si>
-    <t>レポートを識別するビジネス識別子  
-【JP Core仕様】当該検査項目に対して、施設内で割り振られる一位の識別子があればそちらを使用する。</t>
+    <t>レポートを識別するビジネス識別子 【JP Core仕様】当該検査項目に対して、施設内で割り振られる一位の識別子があればそちらを使用する。</t>
   </si>
   <si>
     <t>例：電子カルテ等のオーダ番号、レポート番号、実施日に連番を付加した番号など</t>
@@ -522,8 +521,7 @@
 </t>
   </si>
   <si>
-    <t>元になった検査や診断の依頼  
-【JP Core仕様】オーダ発生元のServiceRequestまたはCarePlanへの参照</t>
+    <t>元になった検査や診断の依頼  【JP Core仕様】オーダ発生元のServiceRequestまたはCarePlanへの参照</t>
   </si>
   <si>
     <t>通常、１結果ごとに１つの検査依頼があるが、状況によっては、複数の検査要求に対して１レポートがある場合がある。また１つの検査依頼に対して複数のレポートが作成される場合もあることに注意。</t>
@@ -544,8 +542,7 @@
     <t>DiagnosticReport.status</t>
   </si>
   <si>
-    <t>診断レポートのステータス  
-【JP Core仕様】レポートの記載状況をバインディングされたコードセットから必ず一つ選ぶ。</t>
+    <t>診断レポートのステータス  【JP Core仕様】レポートの記載状況をバインディングされたコードセットから必ず一つ選ぶ。</t>
   </si>
   <si>
     <t>診断サービスは、暫定/不完全なレポートを日常的に発行し、以前にリリースされたレポートを撤回することもあります。 / Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
@@ -912,8 +909,7 @@
 </t>
   </si>
   <si>
-    <t>レポートの対象、常にではないが、通常は患者  
-【JP Core仕様】Patientリソースを参照</t>
+    <t>レポートの対象、常にではないが、通常は患者  【JP Core仕様】Patientリソースを参照</t>
   </si>
   <si>
     <t>レポートの対象、通常、Patientリソースへの参照。ただし、他のさまざまなソースから収集された検体を対象とすることもある。参照は内容に辿り着ける（解決できる）必要がある（アクセス制御、一時的な使用不可などを考慮に入れる）。解決は、URLから取得するか、リソースタイプによって該当する場合は、絶対参照を正規URLとして扱い、ローカルレジストリ/リポジトリで検索することによって行うことができる。</t>
@@ -945,8 +941,7 @@
 </t>
   </si>
   <si>
-    <t>依頼時におけるヘルスケアイベント（受診など）  
-【JP Core仕様】このレポートを書く切っ掛けとなるEncounterリソースを参照</t>
+    <t>依頼時におけるヘルスケアイベント（受診など） 【JP Core仕様】このレポートを書く切っ掛けとなるEncounterリソースを参照</t>
   </si>
   <si>
     <t>例：診療、歯科健診（検診）、身元不明者調査 ※JP Coreに網羅されていない</t>
@@ -978,8 +973,7 @@
 </t>
   </si>
   <si>
-    <t>臨床的に関連する時刻または時間  
-【JP Core仕様】レポート作成日時</t>
+    <t>臨床的に関連する時刻または時間  【JP Core仕様】レポート作成日時</t>
   </si>
   <si>
     <t>観測値が関連する時間または期間。レポートの対象が患者である場合、これは通常、読影開始の時間であり、日付／時刻自体のみ提供される。実施日時。</t>
@@ -1011,8 +1005,7 @@
 </t>
   </si>
   <si>
-    <t>このバージョンが作成された日時  
-【JP Core仕様】最新のレポート確定日時</t>
+    <t>このバージョンが作成された日時  【JP Core仕様】最新のレポート確定日時</t>
   </si>
   <si>
     <t>通常、レポートがレビューおよび検証・確定された後となる。リソース自体の更新時刻とは異なる場合がある。これは、レポートの実際の提供時刻ではなく、リソース自体の更新時刻はレコード（場合によってはセカンダリコピー）のステータスの更新時刻となるため。</t>
@@ -1041,8 +1034,7 @@
 </t>
   </si>
   <si>
-    <t>レポート内容に責任をもつ診断的サービス  
-【JP Core仕様】レポート確定者</t>
+    <t>レポート内容に責任をもつ診断的サービス  【JP Core仕様】レポート確定者</t>
   </si>
   <si>
     <t>例：歯科医師など</t>
@@ -1070,8 +1062,7 @@
 Reported by</t>
   </si>
   <si>
-    <t>結果の一次解釈者  
-【JP Core仕様】レポートの作成者</t>
+    <t>結果の一次解釈者  【JP Core仕様】レポートの作成者</t>
   </si>
   <si>
     <t>例：歯科医師、歯科研修医など</t>
@@ -1087,8 +1078,7 @@
 </t>
   </si>
   <si>
-    <t>診断レポートのもとになった検体に関する情報  
-【JP Core仕様】未使用</t>
+    <t>診断レポートのもとになった検体に関する情報  【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>検査結果名称のコードを見れば検体情報が十分に判明するような場合には、この検体情報は冗長になる。複数の検体が関与する場合には、検査や検査グループごとに検体情報が記述されることがある。</t>
@@ -1111,8 +1101,7 @@
 </t>
   </si>
   <si>
-    <t>診断レポートの一部となるObservationsに関する情報  
-【JP Core仕様】検査結果</t>
+    <t>診断レポートの一部となるObservationsに関する情報  【JP Core仕様】検査結果</t>
   </si>
   <si>
     <t>Observationsは階層構造を持てる。</t>
@@ -1154,8 +1143,7 @@
 </t>
   </si>
   <si>
-    <t>診断レポートに関連づけられたメディアに関する情報  
-【JP Core仕様】このレポートに関連づけられたキー画像</t>
+    <t>診断レポートに関連づけられたメディアに関する情報  【JP Core仕様】このレポートに関連づけられたキー画像</t>
   </si>
   <si>
     <t>通常は画像。診断プロセス中に作成され、患者から直接取得されたもの、あるいは調製された検体標本（つまり、関心のあるスライド）のこともある。</t>
@@ -1235,8 +1223,7 @@
 </t>
   </si>
   <si>
-    <t>簡潔かつ臨床的な文脈で表現した診断レポートの要約結論（解釈、インプレッション）  
-【JP Core仕様】原則、未使用。レセプト傷病名などテキスト型で記載も可能。</t>
+    <t>簡潔かつ臨床的な文脈で表現した診断レポートの要約結論（解釈、インプレッション） 【JP Core仕様】原則、未使用。レセプト傷病名などテキスト型で記載も可能。</t>
   </si>
   <si>
     <t>基本的な結果データの中で失われない結論を提供できる必要があります。 / Need to be able to provide a conclusion that is not lost among the basic result data.</t>
@@ -1251,8 +1238,7 @@
     <t>DiagnosticReport.conclusionCode</t>
   </si>
   <si>
-    <t>診断レポートの要約結論（解釈、インプレッション）を表すコード  
-【JP Core仕様】原則、未使用。レセプト傷病名などのCodeableConcept型で定義も可能。</t>
+    <t>診断レポートの要約結論（解釈、インプレッション）を表すコード  【JP Core仕様】原則、未使用。レセプト傷病名などのCodeableConcept型で定義も可能。</t>
   </si>
   <si>
     <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、独自の構造を提供する必要がある。</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -376,7 +376,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -592,7 +592,7 @@
     <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -1074,7 +1074,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1119,7 +1119,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ImagingStudy)
+    <t xml:space="preserve">Reference(ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -1200,7 +1200,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media)
+    <t xml:space="preserve">Reference(Media|4.0.1)
 </t>
   </si>
   <si>
@@ -1247,7 +1247,7 @@
     <t>レポートの補助として提供される診断コード。 / Diagnosis codes provided as adjuncts to the report.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="398">
   <si>
     <t>Property</t>
   </si>
@@ -595,7 +595,7 @@
     <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -841,9 +841,6 @@
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.version</t>
@@ -5210,7 +5207,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>266</v>
+        <v>81</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>81</v>
@@ -5281,7 +5278,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>219</v>
@@ -5395,7 +5392,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>226</v>
@@ -5438,10 +5435,10 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>269</v>
+        <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>
@@ -5509,7 +5506,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>232</v>
@@ -5623,7 +5620,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>238</v>
@@ -5739,7 +5736,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>247</v>
@@ -5855,14 +5852,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5884,10 +5881,10 @@
         <v>179</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5899,7 +5896,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -5918,7 +5915,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -5936,7 +5933,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>91</v>
@@ -5951,28 +5948,28 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>281</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5991,19 +5988,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M39" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6052,7 +6049,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6067,28 +6064,28 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>291</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6107,19 +6104,19 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6168,7 +6165,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6183,28 +6180,28 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>301</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6223,19 +6220,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6284,7 +6281,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6299,28 +6296,28 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>311</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6339,19 +6336,19 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6400,7 +6397,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6418,25 +6415,25 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>320</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6455,19 +6452,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -6516,7 +6513,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6531,28 +6528,28 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6571,19 +6568,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>334</v>
-      </c>
       <c r="O44" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6632,7 +6629,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6647,24 +6644,24 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6687,19 +6684,19 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M45" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -6748,7 +6745,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6766,10 +6763,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -6777,14 +6774,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6803,19 +6800,19 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -6864,7 +6861,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6882,10 +6879,10 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -6893,10 +6890,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6919,16 +6916,16 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6978,7 +6975,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6999,7 +6996,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7007,14 +7004,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7033,19 +7030,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7094,7 +7091,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7112,10 +7109,10 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7123,10 +7120,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7235,10 +7232,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7349,14 +7346,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7378,10 +7375,10 @@
         <v>137</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>140</v>
@@ -7436,7 +7433,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7465,10 +7462,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7494,16 +7491,16 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7552,7 +7549,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7573,7 +7570,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -7581,10 +7578,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7607,16 +7604,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7666,7 +7663,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>91</v>
@@ -7687,7 +7684,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -7695,14 +7692,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7724,14 +7721,14 @@
         <v>191</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -7780,7 +7777,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7798,10 +7795,10 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -7809,10 +7806,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7838,13 +7835,13 @@
         <v>179</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7873,11 +7870,11 @@
         <v>182</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
       </c>
@@ -7894,7 +7891,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7912,10 +7909,10 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -7923,10 +7920,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7949,19 +7946,19 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8010,7 +8007,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8028,10 +8025,10 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -273,7 +273,7 @@
 【JP Core仕様】口腔診査結果レポートのプロファイル</t>
   </si>
   <si>
-    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。
+    <t>これは単一のレポートを格納することを目的としており、複数のレポートを含む要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。
 【JP Core仕様】DiagnosticReportリソースの共通プロファイル</t>
   </si>
   <si>
@@ -938,7 +938,7 @@
 </t>
   </si>
   <si>
-    <t>依頼時におけるヘルスケアイベント（受診など） 【JP Core仕様】このレポートを書く切っ掛けとなるEncounterリソースを参照</t>
+    <t>依頼時における診療イベント（受診など） 【JP Core仕様】このレポートを書く切っ掛けとなるEncounterリソースを参照</t>
   </si>
   <si>
     <t>例：診療、歯科健診（検診）、身元不明者調査 ※JP Coreに網羅されていない</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -822,6 +822,15 @@
     <t>【JP Core仕様】レポートカテゴリーとして、LoincコードのLP31759-1（歯科口腔）を使用する。</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="LP31759-1"/&gt;
+    &lt;display value="歯科口腔"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
@@ -847,9 +856,6 @@
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.code</t>
-  </si>
-  <si>
-    <t>LP31759-1</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.display</t>
@@ -4528,7 +4534,7 @@
         <v>81</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>81</v>
+        <v>259</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>81</v>
@@ -4547,7 +4553,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4594,7 +4600,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>190</v>
@@ -4706,7 +4712,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>196</v>
@@ -4820,7 +4826,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>201</v>
@@ -4936,7 +4942,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>210</v>
@@ -5048,7 +5054,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>211</v>
@@ -5162,7 +5168,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>212</v>
@@ -5278,7 +5284,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>219</v>
@@ -5392,7 +5398,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>226</v>
@@ -5438,7 +5444,7 @@
         <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>268</v>
+        <v>81</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="396">
   <si>
     <t>Property</t>
   </si>
@@ -586,13 +586,7 @@
     <t>これは、検索、並べ替え、および表示の目的で使用される。</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -831,9 +825,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
-  </si>
-  <si>
     <t>DiagnosticReport.category:first.id</t>
   </si>
   <si>
@@ -1245,6 +1236,9 @@
   </si>
   <si>
     <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、独自の構造を提供する必要がある。</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>レポートの補助として提供される診断コード。 / Diagnosis codes provided as adjuncts to the report.</t>
@@ -3177,26 +3171,24 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y14" s="2"/>
+      <c r="Z14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB14" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>177</v>
@@ -3217,21 +3209,21 @@
         <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3254,13 +3246,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3311,7 +3303,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3332,7 +3324,7 @@
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
@@ -3340,10 +3332,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3372,7 +3364,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -3413,19 +3405,19 @@
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3446,7 +3438,7 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
@@ -3454,10 +3446,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3480,19 +3472,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3541,7 +3533,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3559,10 +3551,10 @@
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>81</v>
@@ -3570,10 +3562,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3596,13 +3588,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3653,7 +3645,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3674,7 +3666,7 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
@@ -3682,10 +3674,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3714,7 +3706,7 @@
         <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>140</v>
@@ -3755,19 +3747,19 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3788,7 +3780,7 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -3796,10 +3788,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3825,16 +3817,16 @@
         <v>105</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -3883,7 +3875,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3901,10 +3893,10 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -3912,10 +3904,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3938,16 +3930,16 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3997,7 +3989,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4015,10 +4007,10 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4026,10 +4018,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4055,14 +4047,14 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4111,7 +4103,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4129,10 +4121,10 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4140,10 +4132,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4166,17 +4158,17 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -4225,7 +4217,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4243,10 +4235,10 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -4254,10 +4246,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4280,19 +4272,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4341,7 +4333,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4359,10 +4351,10 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -4370,10 +4362,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4396,19 +4388,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -4457,7 +4449,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4475,10 +4467,10 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4486,13 +4478,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>177</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>178</v>
@@ -4517,13 +4509,13 @@
         <v>179</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4534,7 +4526,7 @@
         <v>81</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>81</v>
@@ -4553,7 +4545,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>260</v>
+        <v>182</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4589,21 +4581,21 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>189</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4626,13 +4618,13 @@
         <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4683,7 +4675,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4704,7 +4696,7 @@
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -4712,10 +4704,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4744,7 +4736,7 @@
         <v>138</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>140</v>
@@ -4785,19 +4777,19 @@
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4818,7 +4810,7 @@
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -4826,10 +4818,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4852,19 +4844,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -4913,7 +4905,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4931,10 +4923,10 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -4942,10 +4934,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4968,13 +4960,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5025,7 +5017,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5046,7 +5038,7 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5054,10 +5046,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5086,7 +5078,7 @@
         <v>138</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>140</v>
@@ -5127,19 +5119,19 @@
         <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5160,7 +5152,7 @@
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5168,10 +5160,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5197,16 +5189,16 @@
         <v>105</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O32" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -5255,7 +5247,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5273,10 +5265,10 @@
         <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
@@ -5284,10 +5276,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5310,16 +5302,16 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5369,7 +5361,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5387,10 +5379,10 @@
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
@@ -5398,10 +5390,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5427,14 +5419,14 @@
         <v>111</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -5483,7 +5475,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5501,10 +5493,10 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -5512,10 +5504,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5538,17 +5530,17 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -5597,7 +5589,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5615,10 +5607,10 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -5626,10 +5618,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5652,19 +5644,19 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5713,7 +5705,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5731,10 +5723,10 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -5742,10 +5734,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5768,19 +5760,19 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -5829,7 +5821,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5847,10 +5839,10 @@
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -5858,14 +5850,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5887,10 +5879,10 @@
         <v>179</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5902,7 +5894,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -5921,7 +5913,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -5939,7 +5931,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>91</v>
@@ -5954,28 +5946,28 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>280</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5994,19 +5986,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="O39" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6055,7 +6047,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6070,28 +6062,28 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6110,19 +6102,19 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O40" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6171,7 +6163,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6186,28 +6178,28 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>300</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6226,19 +6218,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O41" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6287,7 +6279,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6302,28 +6294,28 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>310</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6342,19 +6334,19 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O42" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6403,7 +6395,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6421,25 +6413,25 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6458,19 +6450,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -6519,7 +6511,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6534,28 +6526,28 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>329</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6574,19 +6566,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6635,7 +6627,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6650,24 +6642,24 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>329</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6690,19 +6682,19 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="O45" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -6751,7 +6743,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6769,10 +6761,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -6780,14 +6772,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6806,19 +6798,19 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O46" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -6867,7 +6859,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6885,10 +6877,10 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -6896,10 +6888,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6922,16 +6914,16 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6981,7 +6973,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7002,7 +6994,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7010,14 +7002,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7036,19 +7028,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7097,7 +7089,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7115,10 +7107,10 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7126,10 +7118,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7152,13 +7144,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7209,7 +7201,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7230,7 +7222,7 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -7238,10 +7230,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7270,7 +7262,7 @@
         <v>138</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>140</v>
@@ -7323,7 +7315,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7344,7 +7336,7 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -7352,14 +7344,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7381,10 +7373,10 @@
         <v>137</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>140</v>
@@ -7439,7 +7431,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7468,10 +7460,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7494,19 +7486,19 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7555,7 +7547,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7576,7 +7568,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -7584,10 +7576,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7610,16 +7602,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7669,7 +7661,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>91</v>
@@ -7690,7 +7682,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -7698,14 +7690,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7724,17 +7716,17 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -7783,7 +7775,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7801,10 +7793,10 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -7812,10 +7804,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7841,13 +7833,13 @@
         <v>179</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7873,13 +7865,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>182</v>
+        <v>386</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -7897,7 +7889,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7915,10 +7907,10 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -7926,10 +7918,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7952,19 +7944,19 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8013,7 +8005,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8031,10 +8023,10 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
